--- a/employment_forms/050_hospitality_part_time_employment_form--employment_forms.xlsx
+++ b/employment_forms/050_hospitality_part_time_employment_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'night'}</t>
+          <t>night</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Night'}</t>
+          <t>Night</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'entry_level'}</t>
+          <t>entry_level</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Entry Level'}</t>
+          <t>Entry Level</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'mid-level'}</t>
+          <t>mid-level</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Mid-level'}</t>
+          <t>Mid-level</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'senior'}</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Senior'}</t>
+          <t>Senior</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
